--- a/sistema de registro de docentes/Resources/materias.xlsx
+++ b/sistema de registro de docentes/Resources/materias.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROYECTO\proyecto registro de asistencia profesores\sistema de registro de docentes\sistema de registro de docentes\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECE63FB-3DF2-4FC5-B362-F4C54236151A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ING. DE SISTEMAS" sheetId="5" r:id="rId1"/>
-    <sheet name="ING. DE SIS. ELECTRONICOS" sheetId="6" r:id="rId2"/>
+    <sheet name="ING. MECATRONICA" sheetId="7" r:id="rId2"/>
+    <sheet name="ING. EN TELECOMUNICACIONES" sheetId="8" r:id="rId3"/>
+    <sheet name="ING. DE SIS. ELECTRONICOS" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="181">
   <si>
     <t>Tercer Semestre</t>
   </si>
@@ -42,12 +43,6 @@
     <t>Cuarto Semestre</t>
   </si>
   <si>
-    <t>Primer Semestre</t>
-  </si>
-  <si>
-    <t>Segundo Semestre</t>
-  </si>
-  <si>
     <t>Quinto Semestre</t>
   </si>
   <si>
@@ -222,34 +217,373 @@
     <t>REALIDADNAL.Y FF.AA. EN APOYO AL DES. NAL.</t>
   </si>
   <si>
-    <t>TERCER SEMESTRE</t>
-  </si>
-  <si>
-    <t>CUARTO SEMESTRE</t>
-  </si>
-  <si>
-    <t>QUINTO SEMESTRE</t>
-  </si>
-  <si>
-    <t>SEXTO SEMESTRE</t>
-  </si>
-  <si>
-    <t>SEPTIMO SEMESTRE</t>
-  </si>
-  <si>
-    <t>OCTAVO SEMESTRE</t>
-  </si>
-  <si>
-    <t>NOVENO SEMESTRE</t>
-  </si>
-  <si>
-    <t>DECIMO SEMESTRE</t>
+    <t>3RO.</t>
+  </si>
+  <si>
+    <t>4TO.</t>
+  </si>
+  <si>
+    <t>5TO.</t>
+  </si>
+  <si>
+    <t>6TO.</t>
+  </si>
+  <si>
+    <t>7MO.</t>
+  </si>
+  <si>
+    <t>8VO.</t>
+  </si>
+  <si>
+    <t>9NO.</t>
+  </si>
+  <si>
+    <t>10MO.</t>
+  </si>
+  <si>
+    <t>ANALISIS DE CIRCUITOS</t>
+  </si>
+  <si>
+    <t>ECUACIONES DIFERENCIALES</t>
+  </si>
+  <si>
+    <t>METODOLOGÍA DE LA INVESTIGACIÓN</t>
+  </si>
+  <si>
+    <t>PROGRAMACIÓN II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARIABLE COMPLEJA           </t>
+  </si>
+  <si>
+    <t>INVESTIGACIÓN OPERATIVA I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELECTRONICA ANALÓGICA I </t>
+  </si>
+  <si>
+    <t>SISTEMAS DIGITALES I</t>
+  </si>
+  <si>
+    <t>SINTESIS DE CIRCUITOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METODOS NUMERICOS </t>
+  </si>
+  <si>
+    <t>GRAL. PL. MY - LOGISTICA - SS.PP.UU</t>
+  </si>
+  <si>
+    <t>SISTEMAS DIGITALES II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEÑALES Y SISTEMAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECANISMOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELECTRONICA ANALOGICA II </t>
+  </si>
+  <si>
+    <t>HISTORIA Y GEOGRAFIA MILITAR APLICADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIGACIÓN OPERATIVA II </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESISTENCIA DE MATERIALES </t>
+  </si>
+  <si>
+    <t>ECONOMIA PARA LA INGENIERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELECTRONICA ANALÓGICA III </t>
+  </si>
+  <si>
+    <t>TERMODINÁMICA Y TRANS.DE CALOR</t>
+  </si>
+  <si>
+    <t>DISEÑO MECANICO I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISTEMAS DE CONTROL I </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICROPROCESADORES I </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEGISLACION PARA INGENIERIA </t>
+  </si>
+  <si>
+    <t>MICROPROCESADORES II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISTEMAS DE CONTROL II </t>
+  </si>
+  <si>
+    <t>MODELADO Y SIMULACION DE SISTEMAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISEÑO MECANICO II </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBOTICA  MOVIL </t>
+  </si>
+  <si>
+    <t>LEGISLACION MILITAR, DD.HH - DIH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISTEMAS EMBEBIDOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISTEMAS INTELIGENTES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESAMIENTO DIGITAL DE SEÑALES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIBRACIONES MECANICAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBOTICA  INDUSTRIAL </t>
+  </si>
+  <si>
+    <t>PREPARACION Y EVELUACION DE PROYECTOS</t>
+  </si>
+  <si>
+    <t>MAQUINAS HIDRAULICAS Y NEUMATICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOMATIZACION INDUSTRIAL </t>
+  </si>
+  <si>
+    <t>REGULACION INDUSTRIAL</t>
+  </si>
+  <si>
+    <t>PROTOTIPADO RAPIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUFACTURA INTEGRADA </t>
+  </si>
+  <si>
+    <t>TRABAJO DE GRADO II</t>
+  </si>
+  <si>
+    <t>SEMINARIO DE CONTROL AVANZADO</t>
+  </si>
+  <si>
+    <t>SEMINARIO DE DISEÑO E INNOVACIÓN TECNOLÓGICA</t>
+  </si>
+  <si>
+    <t>VISIÓN COMPUTACIONAL</t>
+  </si>
+  <si>
+    <t>REALIDAD NAL. Y FF.AA. EN APOYO AL DES. NAL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPONENTES E INSTRUMENTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">METODOLOGÍA DE LA INVESTIGACIÓN </t>
+  </si>
+  <si>
+    <t>BFE. COA. TAC. GENERAL</t>
+  </si>
+  <si>
+    <t>CAMPOS ELECTROMAGNÉTICOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIGACIÓN OPERATIVA </t>
+  </si>
+  <si>
+    <t>PROGRAMACIÓN DE SISTEMAS I</t>
+  </si>
+  <si>
+    <t>ELECTRÓNICA ANALÓGICA II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROGRAMACIÓN DE SISTEMAS II </t>
+  </si>
+  <si>
+    <t>LINEAS DE TRANSMISION Y ANTENAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSMISIÓN DE DATOS I </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELECTRONICA DIGITAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSMISION DE DATOS  II </t>
+  </si>
+  <si>
+    <t>ECONOMIA PARA INGENIERIA</t>
+  </si>
+  <si>
+    <t>MICROPROCESADORES</t>
+  </si>
+  <si>
+    <t>ELECTRONICA ANALOGICA III</t>
+  </si>
+  <si>
+    <t>SISTEMAS  DE COMUNICACIÓN I</t>
+  </si>
+  <si>
+    <t>SISTEMAS DE MODELADO Y SIMULACIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISTEMAS DE COMUNICACIÓN III </t>
+  </si>
+  <si>
+    <t>INGENIERIA DE CONTROL</t>
+  </si>
+  <si>
+    <t>LEGISLACIÓN PARA INGENIERÍA</t>
+  </si>
+  <si>
+    <t>COMUNICACIONES MOVILES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMUNICACIONES OPTICAS </t>
+  </si>
+  <si>
+    <t>REDES DE COMPUTACION</t>
+  </si>
+  <si>
+    <t>PREPARACION Y EVALUACION DE PROYECTOS</t>
+  </si>
+  <si>
+    <t>COMUNICACIONES SATELITALES</t>
+  </si>
+  <si>
+    <t>PROCESAMIENTO DIGITAL DE SEÑALES</t>
+  </si>
+  <si>
+    <t>SISTEMAS DE COMUNICACIÓN III</t>
+  </si>
+  <si>
+    <t>SISTEMAS MULTIMEDIA Y DIFUSION</t>
+  </si>
+  <si>
+    <t>INGENIERIA TELEMATICA I</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TRABAJO DE GRADO I </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROCESAMIENTO DIGITAL DE SEÑALES II </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGENIERÍA DE TRÁFICO </t>
+  </si>
+  <si>
+    <t>INGENIERÍA TELMÁTICA II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISTEMAS Y SERVICIOS DIGITALES  </t>
+  </si>
+  <si>
+    <t>VARIABLE COMPLEJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADISTICA II </t>
+  </si>
+  <si>
+    <t>COMPONENTES E INSTRUMENTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALISIS DE CIRCUITOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISTEMAS DIGITALES I </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPOS ELECTROMAGNÉTICOS </t>
+  </si>
+  <si>
+    <t>INVESTIGACIÓN OPERATIVA</t>
+  </si>
+  <si>
+    <t>ELECTRONICA ANALÓGICA I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CON. ELECTROMAGNETICA DE ENERGIÍA  </t>
+  </si>
+  <si>
+    <t>SEÑALES Y SISTEMAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELECTRONICA ANALOGICA III </t>
+  </si>
+  <si>
+    <t>PROPAGACIÓN Y ENLACES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONMUTACIÓN DIGITAL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELECOMUNICACIONES I </t>
+  </si>
+  <si>
+    <t>LEGISLACIÓN PARA LA INGENIERIA</t>
+  </si>
+  <si>
+    <t>SISTEMAS DE COMPUTACIÓN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MICROPROCESADORES  II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELECTRONICA INDUSTRIAL I </t>
+  </si>
+  <si>
+    <t>ELECTRÓNICA INDUSTRIAL II</t>
+  </si>
+  <si>
+    <t>PREPARACIÓN Y EVALUACIÓN DE PROYECTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELECOMUNICACIONES II (T) </t>
+  </si>
+  <si>
+    <t>REDES DE COMUNICACIÓN I</t>
+  </si>
+  <si>
+    <t>CONTROL Y REGULACIÓN INDUSTRIAL I</t>
+  </si>
+  <si>
+    <t>CONTROL Y REGULACIÓN INDUSTRIAL II</t>
+  </si>
+  <si>
+    <t>SISTEMAS ENERGETICOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELECOMUNICACIONES III </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDES DE COMUNICACIÓN II </t>
+  </si>
+  <si>
+    <t>SISTEMAS DE CONTROL INDUSTRIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TRABAJO DE GRADO II</t>
+  </si>
+  <si>
+    <t>TELECOMUNICACIONES AVANZADAS</t>
+  </si>
+  <si>
+    <t>TELEMATICA</t>
+  </si>
+  <si>
+    <t>ELECTROMEDICINA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -281,11 +615,6 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -321,8 +650,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -443,8 +778,98 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF66FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B2DE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA187E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -491,119 +916,214 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{CB7EA4BA-F587-431E-B764-0BBDEDB4781F}"/>
-    <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 3" xfId="3" xr:uid="{0E26D87F-ECF7-4F1F-AEFC-D1FA0657BE14}"/>
-    <cellStyle name="Normal 4" xfId="4" xr:uid="{B8B740DF-4EA7-4604-853B-F798C6A956BC}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2 2" xfId="1"/>
+    <cellStyle name="Normal 3" xfId="3"/>
+    <cellStyle name="Normal 4" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -880,248 +1400,248 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{534D26E8-8FF6-4A1F-B862-3E7EEC9CA17A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.5546875" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" customWidth="1"/>
-    <col min="5" max="5" width="32.88671875" customWidth="1"/>
-    <col min="6" max="6" width="31.5546875" customWidth="1"/>
-    <col min="7" max="7" width="29.109375" customWidth="1"/>
-    <col min="8" max="8" width="26.77734375" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+    </row>
+    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="C8" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D8" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E8" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="36"/>
-    </row>
-    <row r="7" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-    </row>
-    <row r="8" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="26" t="s">
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G15" s="1"/>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B9">
+  <sortState ref="B3:B9">
     <sortCondition ref="B2:B9"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1130,34 +1650,470 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F9BD4D-FC45-47D6-99B5-9047DD6965C9}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" customWidth="1"/>
-    <col min="7" max="7" width="24.77734375" customWidth="1"/>
-    <col min="8" max="8" width="23.5546875" customWidth="1"/>
-    <col min="9" max="9" width="24.6640625" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="29"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="37"/>
+    </row>
+    <row r="7" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="29"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
@@ -1171,118 +2127,216 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="10"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-    </row>
-    <row r="2" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="8"/>
+    </row>
+    <row r="2" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-    </row>
-    <row r="3" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="9"/>
+    </row>
+    <row r="3" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-    </row>
-    <row r="4" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="9"/>
+    </row>
+    <row r="4" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="G4" s="54" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
       <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="9"/>
+    </row>
+    <row r="5" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="54" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="9"/>
+    </row>
+    <row r="6" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="9"/>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E20" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="F7" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="62"/>
+      <c r="D8" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="62"/>
+      <c r="H8" s="29"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sistema de registro de docentes/Resources/materias.xlsx
+++ b/sistema de registro de docentes/Resources/materias.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROYECTO\proyecto registro de asistencia profesores\sistema de registro de docentes\sistema de registro de docentes\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A740DC-16F7-433F-A4F6-334021397F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ING. DE SISTEMAS" sheetId="5" r:id="rId1"/>
@@ -18,48 +19,11 @@
     <sheet name="ING. DE SIS. ELECTRONICOS" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="181">
-  <si>
-    <t>Tercer Semestre</t>
-  </si>
-  <si>
-    <t>Cuarto Semestre</t>
-  </si>
-  <si>
-    <t>Quinto Semestre</t>
-  </si>
-  <si>
-    <t>Sexto Semestre</t>
-  </si>
-  <si>
-    <t>Septimo Semestre</t>
-  </si>
-  <si>
-    <t>Octavo Semestre</t>
-  </si>
-  <si>
-    <t>Noveno Semestre</t>
-  </si>
-  <si>
-    <t>Decimo Semestre</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="173">
   <si>
     <t>ESTADISTICA II</t>
   </si>
@@ -583,7 +547,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1120,10 +1084,10 @@
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="1"/>
-    <cellStyle name="Normal 3" xfId="3"/>
-    <cellStyle name="Normal 4" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1400,222 +1364,222 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="29.140625" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="32.88671875" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" customWidth="1"/>
+    <col min="7" max="7" width="29.109375" customWidth="1"/>
+    <col min="8" max="8" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="C3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="H3" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="D6" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F6" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>49</v>
       </c>
       <c r="G6" s="30"/>
       <c r="H6" s="31"/>
     </row>
-    <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G7" s="29"/>
       <c r="H7" s="29"/>
     </row>
-    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G8" s="29"/>
       <c r="H8" s="29"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
@@ -1624,24 +1588,24 @@
       <c r="G9" s="29"/>
       <c r="H9" s="29"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G15" s="1"/>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="B3:B9">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B9">
     <sortCondition ref="B2:B9"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1650,692 +1614,692 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="29.140625" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="32.88671875" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" customWidth="1"/>
+    <col min="7" max="7" width="29.109375" customWidth="1"/>
+    <col min="8" max="8" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B7" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="28" t="s">
+      <c r="B8" s="26" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="19" t="s">
+      <c r="C8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="H7" s="29"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="35" t="s">
-        <v>102</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H8" s="29"/>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" customWidth="1"/>
-    <col min="7" max="7" width="29.140625" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.44140625" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="32.88671875" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" customWidth="1"/>
+    <col min="7" max="7" width="29.109375" customWidth="1"/>
+    <col min="8" max="8" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="B5" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="37"/>
+    </row>
+    <row r="7" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C8" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="11"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="E8" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="H6" s="37"/>
-    </row>
-    <row r="7" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="H7" s="29"/>
-    </row>
-    <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>142</v>
-      </c>
       <c r="H8" s="29"/>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.5546875" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="5"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="46" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="G3" s="40" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H3" s="42" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="5"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="51" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B4" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="53" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E4" s="53" t="s">
-        <v>163</v>
-      </c>
       <c r="F4" s="53" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G4" s="54" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="5"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="55" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="G5" s="56" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="5"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="54" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="5"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="57" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D7" s="59" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E7" s="60" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F7" s="61" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>15</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>23</v>
       </c>
       <c r="C8" s="62"/>
       <c r="D8" s="22" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="G8" s="62"/>
       <c r="H8" s="29"/>
     </row>
-    <row r="9" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E15" s="1"/>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
     </row>
   </sheetData>

--- a/sistema de registro de docentes/Resources/materias.xlsx
+++ b/sistema de registro de docentes/Resources/materias.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROYECTO\proyecto registro de asistencia profesores\sistema de registro de docentes\sistema de registro de docentes\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A740DC-16F7-433F-A4F6-334021397F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5882E475-1CDC-4E2A-A46A-887B1917169E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ING. DE SISTEMAS" sheetId="5" r:id="rId1"/>
     <sheet name="ING. MECATRONICA" sheetId="7" r:id="rId2"/>
-    <sheet name="ING. EN TELECOMUNICACIONES" sheetId="8" r:id="rId3"/>
-    <sheet name="ING. DE SIS. ELECTRONICOS" sheetId="6" r:id="rId4"/>
+    <sheet name="ING. DE TELECOMUNICACIONES" sheetId="8" r:id="rId3"/>
+    <sheet name="ING. DE SISTEMAS ELECTRONICOS" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
